--- a/sheet_metal/bend_parameters.xlsx
+++ b/sheet_metal/bend_parameters.xlsx
@@ -5,6 +5,7 @@
   <sheets>
     <sheet state="visible" name="Excel 連動板金計算器" sheetId="1" r:id="rId5"/>
     <sheet state="visible" name="Hardware" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Special" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -12,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
   <si>
     <t>材質 / 厚度</t>
   </si>
@@ -60,6 +61,30 @@
   </si>
   <si>
     <t>拉釘 (鉚釘)</t>
+  </si>
+  <si>
+    <t>折彎類型 / 厚度</t>
+  </si>
+  <si>
+    <t>備註</t>
+  </si>
+  <si>
+    <t>圓弧折 (R5)</t>
+  </si>
+  <si>
+    <t>經驗值</t>
+  </si>
+  <si>
+    <t>死邊 (Hem)</t>
+  </si>
+  <si>
+    <t>延伸縮減</t>
+  </si>
+  <si>
+    <t>Z型對折</t>
+  </si>
+  <si>
+    <t>段差補償</t>
   </si>
 </sst>
 </file>
@@ -120,6 +145,10 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -527,4 +556,84 @@
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D1" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="D2" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="1">
+        <v>-0.5</v>
+      </c>
+      <c r="C3" s="1">
+        <v>-0.8</v>
+      </c>
+      <c r="D3" s="1">
+        <v>-1.2</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/sheet_metal/bend_parameters.xlsx
+++ b/sheet_metal/bend_parameters.xlsx
@@ -4,8 +4,9 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="Excel 連動板金計算器" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Hardware" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="Special" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="「Excel 連動板金計算器」的副本" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Hardware" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="Special" sheetId="4" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -13,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
   <si>
     <t>材質 / 厚度</t>
   </si>
@@ -149,6 +150,10 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -451,107 +456,71 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>11</v>
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C1" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E1" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="F1" s="1">
+        <v>4.0</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>3.7</v>
+        <v>0.42</v>
       </c>
       <c r="C2" s="1">
-        <v>4.2</v>
+        <v>0.43</v>
       </c>
       <c r="D2" s="1">
-        <v>4.2</v>
+        <v>0.44</v>
       </c>
       <c r="E2" s="1">
-        <v>5.4</v>
+        <v>0.46</v>
       </c>
       <c r="F2" s="1">
-        <v>6.4</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>13</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>3.7</v>
+        <v>0.35</v>
       </c>
       <c r="C3" s="1">
-        <v>4.2</v>
+        <v>0.36</v>
       </c>
       <c r="D3" s="1">
-        <v>4.2</v>
+        <v>0.38</v>
       </c>
       <c r="E3" s="1">
-        <v>5.4</v>
+        <v>0.4</v>
       </c>
       <c r="F3" s="1">
-        <v>6.4</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>13</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="1">
-        <v>3.3</v>
-      </c>
-      <c r="H4" s="1">
-        <v>4.1</v>
-      </c>
+      <c r="A4" s="2"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -567,6 +536,122 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="1">
+        <v>3.7</v>
+      </c>
+      <c r="C2" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="D2" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="E2" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="F2" s="1">
+        <v>6.4</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1">
+        <v>3.7</v>
+      </c>
+      <c r="C3" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="D3" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="E3" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="F3" s="1">
+        <v>6.4</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="1">
+        <v>3.3</v>
+      </c>
+      <c r="H4" s="1">
+        <v>4.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B1" s="1">
